--- a/data-source/tarot-data.xlsx.xlsx
+++ b/data-source/tarot-data.xlsx.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyCreation\Web\TarotBox\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyCreation\Web\TarotCompass\tarot-compass\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DC1BEBA-9DAC-4320-A73B-E982D217F802}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{136954E9-88B6-4B08-89ED-CBDA9B273B15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5016" yWindow="2592" windowWidth="17280" windowHeight="9648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TarotCard" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="162">
   <si>
     <t>卡片編號</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -519,13 +519,6 @@
   </si>
   <si>
     <t>tarot76.jpg</t>
-  </si>
-  <si>
-    <t>tarotBack.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>死神</t>
@@ -907,7 +900,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E98"/>
+  <dimension ref="A1:E97"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="3" width="18.625" style="2" customWidth="1"/>
@@ -1107,7 +1100,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>102</v>
@@ -1943,90 +1936,82 @@
       <c r="D80" s="7"/>
       <c r="E80" s="7"/>
     </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="2">
-        <v>78</v>
-      </c>
-      <c r="B81" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="C81" s="5" t="s">
-        <v>161</v>
-      </c>
+    <row r="81" spans="3:5">
+      <c r="C81" s="7"/>
       <c r="D81" s="7"/>
       <c r="E81" s="7"/>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="3:5">
       <c r="C82" s="7"/>
       <c r="D82" s="7"/>
       <c r="E82" s="7"/>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="3:5">
       <c r="C83" s="7"/>
       <c r="D83" s="7"/>
       <c r="E83" s="7"/>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="3:5">
       <c r="C84" s="7"/>
       <c r="D84" s="7"/>
       <c r="E84" s="7"/>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" spans="3:5">
       <c r="C85" s="7"/>
       <c r="D85" s="7"/>
       <c r="E85" s="7"/>
     </row>
-    <row r="86" spans="1:5">
+    <row r="86" spans="3:5">
       <c r="C86" s="7"/>
       <c r="D86" s="7"/>
       <c r="E86" s="7"/>
     </row>
-    <row r="87" spans="1:5">
+    <row r="87" spans="3:5">
       <c r="C87" s="7"/>
       <c r="D87" s="7"/>
       <c r="E87" s="7"/>
     </row>
-    <row r="88" spans="1:5">
+    <row r="88" spans="3:5">
       <c r="C88" s="7"/>
       <c r="D88" s="7"/>
       <c r="E88" s="7"/>
     </row>
-    <row r="89" spans="1:5">
+    <row r="89" spans="3:5">
       <c r="C89" s="7"/>
       <c r="D89" s="7"/>
       <c r="E89" s="7"/>
     </row>
-    <row r="90" spans="1:5">
+    <row r="90" spans="3:5">
       <c r="C90" s="7"/>
       <c r="D90" s="7"/>
       <c r="E90" s="7"/>
     </row>
-    <row r="91" spans="1:5">
+    <row r="91" spans="3:5">
       <c r="C91" s="7"/>
       <c r="D91" s="7"/>
       <c r="E91" s="7"/>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" spans="3:5">
       <c r="C92" s="7"/>
       <c r="D92" s="7"/>
       <c r="E92" s="7"/>
     </row>
-    <row r="93" spans="1:5">
+    <row r="93" spans="3:5">
       <c r="C93" s="7"/>
       <c r="D93" s="7"/>
       <c r="E93" s="7"/>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="3:5">
       <c r="C94" s="7"/>
       <c r="D94" s="7"/>
       <c r="E94" s="7"/>
     </row>
-    <row r="95" spans="1:5">
+    <row r="95" spans="3:5">
       <c r="C95" s="7"/>
       <c r="D95" s="7"/>
       <c r="E95" s="7"/>
     </row>
-    <row r="96" spans="1:5">
+    <row r="96" spans="3:5">
       <c r="C96" s="7"/>
       <c r="D96" s="7"/>
       <c r="E96" s="7"/>
@@ -2035,11 +2020,6 @@
       <c r="C97" s="7"/>
       <c r="D97" s="7"/>
       <c r="E97" s="7"/>
-    </row>
-    <row r="98" spans="3:5">
-      <c r="C98" s="7"/>
-      <c r="D98" s="7"/>
-      <c r="E98" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
